--- a/checkrates/week-18/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_7d.xlsx
@@ -17,12 +17,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Channel" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Menor Conv Rate" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan de Acción" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · Críticos" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · BajoRend" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · Críticos" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · BajoRend" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · Críticos" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · BajoRend" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · Sev Ef" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · Sev CV" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · Críticos" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · BajoRend" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2C · Sin Conv" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · Sev Ef" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · Sev CV" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · Críticos" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · BajoRend" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta B2B Opaco · Sin Conv" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · Sev Ef" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · Sev CV" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · Críticos" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · BajoRend" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Canasta CUG · Sin Conv" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -548,7 +557,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -704,7 +713,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -973,6 +982,312 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canasta B2C · Severity Eficacia</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>B2C · P80 · target ≥ 97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Banda</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Rango</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Hoteles</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>&lt;60%</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.02267674522009782</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>60-85%</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.03023566029346376</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>85-93%</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.0493552690084482</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>93-97%</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>264</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.1173855046687417</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>≥97%</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1755</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.7803468208092486</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canasta B2C · Severity Conv Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>B2C · P80 · target ≥ 2,5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Banda</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Rango</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Hoteles</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>BKGS=0</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1921</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.8541574032903513</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>&lt;0,8%</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.02445531347265451</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>0,8-1,5%</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.02445531347265451</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1,5-2,5%</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.02979101823032459</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>≥2,5%</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.06714095153401511</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1010,7 +1325,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3386,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3108,7 +3423,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5329,2256 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canasta B2C · Top 50 Sin Conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>B2C · BKGS=0 · ordenado por CR ↓ · cohorte estructural</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Rk</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>CorpName</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Destino</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>CR_Unicos</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Bookings</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Eficacia</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>BandaEficacia</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>(471666) - Las Vegas Hilton at Resorts World</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>3087</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>223</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>0.07223841917719469</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>(103551) - Holiday Inn Toronto Downtown Centre by IHG</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Toronto Area</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>2426</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>2363</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>0.9740313272877164</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>(102572) - Hyatt Grand Central New York</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>2163</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>2106</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>0.9736477115117892</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>(104809) - Hyatt Regency Toronto</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Toronto Area</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>1928</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>1910</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0.9906639004149378</v>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>(475706) - Conrad Las Vegas at Resorts World</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>208</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>0.1309823677581864</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>(361563) - Hyatt Place San Juan</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>1301</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>1289</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>0.9907763259031515</v>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>(324901) - Paris Las Vegas Resort &amp; Casino</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Caesars Entertainment</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>636</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>0.5260545905707196</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>(102874) - Rio Hotel &amp; Casino</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>1057</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>840</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>0.7947019867549668</v>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>(104885) - Hyatt Regency Vancouver</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>995</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>(111074) - Wyndham Garden Chinatown</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>908</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>884</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>0.973568281938326</v>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>(120758) - Holiday Inn Express Nashville Downtown Conf Ctr, an IHG Hotel</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Nashville (and vicinity), TN, US</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>791</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>754</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>0.9532237673830595</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>(131583) - Holiday Inn Express Toronto - Downtown by IHG</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Toronto Area</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>782</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>773</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>0.9884910485933504</v>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>(102233) - Grand Decameron Complex, A Trademark All-Inclusive</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Decameron</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Riviera Nayarit</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>743</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>349</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>0.4697173620457604</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>(105612) - Hyatt Regency Aruba Resort and Casino</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>736</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>724</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>0.9836956521739131</v>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>(104715) - Hotel Europa, BW Signature Collection</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Best Western</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Montreal</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>727</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>727</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>(103377) - InterContinental New York Barclay by IHG</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>727</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>727</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>(308909) - Hotel 50 Bowery, part of JdV by Hyatt</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>692</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>691</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>0.9985549132947977</v>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>(103830) - Hilton Anaheim</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Anaheim Area</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>690</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>682</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>0.9884057971014493</v>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>(343311) - Hyatt Regency Seattle</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Seattle Area</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>686</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>665</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>0.9693877551020408</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>(111030) - Holiday Inn Express New York - Manhattan West Side by IHG</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>676</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>667</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>0.9866863905325444</v>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>(152097) - Fairmont Nile City, Cairo</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>El Cairo Area</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>662</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>625</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>0.9441087613293051</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>(104932) - Holiday Inn Montréal Centre-Ville Downtown by IHG</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Montreal</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>658</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>650</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>0.9878419452887538</v>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>(113917) - Hyatt Regency Jacksonville</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Jacksonville Area</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>654</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>646</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>0.9877675840978594</v>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>(100014) - Hotel NYX Cancun</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>619</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>619</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>(108547) - Hilton Boston Logan Airport</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>603</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>602</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>0.9983416252072969</v>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>(100037) - Barceló Puerto Vallarta</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Barcelo</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Puerto Vallarta Area</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>572</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>572</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>(103717) - Hyatt Regency London The Churchill</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Londres</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>532</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>523</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>0.9830827067669173</v>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>(100456) - Dreams Sapphire Resort &amp; Spa</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt Inclusive Collection</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Riviera Maya</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>521</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>521</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>(114034) - Grand Hyatt Washington</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Greenville Area</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>514</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>508</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="13" t="n">
+        <v>0.9883268482490273</v>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>(104512) - Hyatt Regency Miami</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Miami Area</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>485</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>481</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="13" t="n">
+        <v>0.9917525773195877</v>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>(110668) - DoubleTree by Hilton Orlando Theme Park Resort</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>462</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>459</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="13" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>(107689) - Beach House Fort Lauderdale, a Hilton Resort</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale (and vicinity), FL, US</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>443</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>442</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="13" t="n">
+        <v>0.9977426636568849</v>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>(103349) - New York Hilton Midtown</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>439</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>432</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="13" t="n">
+        <v>0.9840546697038725</v>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>(124692) - Wyndham Grand Pittsburgh Downtown</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Pittsburgh Area</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>433</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>433</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>(103338) - Hilton Orlando</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>432</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>406</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="13" t="n">
+        <v>0.9398148148148148</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>(114398) - Hyatt Place Tampa Airport/Westshore</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Area</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>420</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>416</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="13" t="n">
+        <v>0.9904761904761905</v>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>(231691) - SAHARA Las Vegas</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>419</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>419</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>(103725) - Washington Hilton</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Greenville Area</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>416</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>414</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="13" t="n">
+        <v>0.9951923076923077</v>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>(108555) - Hyatt Regency Boston/Cambridge</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>405</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>398</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="13" t="n">
+        <v>0.9827160493827161</v>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>(239614) - Hyatt Place Buffalo/Amherst</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Sheridan Area</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>400</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>400</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>(120342) - Kimpton Hotel Vintage Seattle by IHG</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Seattle Area</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>399</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>365</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="13" t="n">
+        <v>0.9147869674185464</v>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>(100038) - Occidental Tucancun</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Barcelo</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>399</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>399</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>(154029) - Holiday Inn Express &amp; Suites Mississauga-Toronto Southwest by IHG</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Toronto Area</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>385</v>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>381</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="13" t="n">
+        <v>0.9896103896103896</v>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>(301215) - DoubleTree by Hilton New York Times Square West</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>382</v>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>374</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="13" t="n">
+        <v>0.9790575916230366</v>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>(162616) - Hyatt Regency Dallas</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>381</v>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>380</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="13" t="n">
+        <v>0.9973753280839895</v>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>(307484) - Hilton West Palm Beach</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>West Palm Beach Area</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>379</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>378</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="13" t="n">
+        <v>0.9973614775725593</v>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>(159619) - Hyatt Place Seattle Downtown</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Seattle Area</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>378</v>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>373</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="13" t="n">
+        <v>0.9867724867724867</v>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>(102025) - Disney's All-Star Music Resort</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Disney</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>374</v>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>372</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="13" t="n">
+        <v>0.9946524064171123</v>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>(108549) - Wyndham Boston Beacon Hill</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>372</v>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>365</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="13" t="n">
+        <v>0.9811827956989247</v>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>(120313) - Grand Hyatt Seattle</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Seattle Area</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>370</v>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>366</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="13" t="n">
+        <v>0.9891891891891892</v>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canasta B2B Opaco · Severity Eficacia</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>B2B (OP) · P80 · target ≥ 97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Banda</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Rango</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Hoteles</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>&lt;60%</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.01654792001838658</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>60-85%</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>369</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.08480809009423121</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>85-93%</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>458</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>93-97%</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>618</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.1420363134911515</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>≥97%</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>2834</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.6513445185014939</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canasta B2B Opaco · Severity Conv Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>B2B (OP) · P80 · target ≥ 2,5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Banda</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Rango</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Hoteles</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>BKGS=0</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1636</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.3760055159733395</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>&lt;0,8%</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>545</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.1252585612502873</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>0,8-1,5%</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>741</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.1703056768558952</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1,5-2,5%</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>533</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.1225005745805562</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>≥2,5%</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>896</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.2059296713399218</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5052,7 +7616,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7113,7 +9677,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7150,7 +9714,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9056,7 +11620,2409 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Severity · ConvRate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>P80 · 4734 hoteles · target ≥ 2,5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Banda</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Rango</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Hoteles</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>BKGS=0</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1342</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.2834811998310097</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>&lt;0,8%</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>813</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.1717363751584284</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>0,8-1,5%</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>789</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1,5-2,5%</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>713</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.1506125897760879</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>≥2,5%</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1077</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.2275031685678074</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canasta B2B Opaco · Top 50 Sin Conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>B2B (OP) · BKGS=0 · ordenado por CR ↓ · cohorte estructural</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Rk</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>CorpName</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Destino</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>CR_Unicos</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Bookings</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Eficacia</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>BandaEficacia</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>(463144) - Hilton Abu Dhabi Yas Island</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>4411</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>4408</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>0.9993198821128996</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>(121779) - Sofitel Cairo Downtown Nile</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>El Cairo Area</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>3304</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>3189</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>0.9651937046004843</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>(532279) - Hilton Cairo Nile Maadi</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>El Cairo Area</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>2923</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>2891</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>0.9890523434827232</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>(471666) - Las Vegas Hilton at Resorts World</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>2861</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>284</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0.09926599091226844</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>(475706) - Conrad Las Vegas at Resorts World</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>2637</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>480</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>0.1820250284414107</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>(276943) - Waldorf Astoria Dubai Palm Jumeirah</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Dubai Area</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>2424</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>0.8663366336633663</v>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>(486497) - TRYP By Wyndham Istanbul Sisli Hotel</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Istanbul Area</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>2003</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>0.9906033630069239</v>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>(121784) - Hilton Cairo Grand Nile</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>El Cairo Area</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>1937</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>1930</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>0.996386164171399</v>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>(520454) - Tribe Amsterdam City</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>1709</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>1661</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>0.9719133996489175</v>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>(111293) - Novotel Paris Centre Tour Eiffel</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>1566</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>1546</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>0.9872286079182631</v>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>(103378) - InterContinental New York Times Square by IHG</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>1414</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>1355</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>0.9582743988684582</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>(121084) - DoubleTree by Hilton Sharm El Sheikh - Sharm Bay</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Sharm el Sheikh Area</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>1359</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>1359</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>(493347) - Hotel Indigo Bali Seminyak Beach by IHG</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>SinClasificar</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>1356</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>1052</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>0.775811209439528</v>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>(280140) - Hilton Batumi</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Adjara Area</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>1301</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>0.9637037037037037</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>(239533) - Park Hyatt New York</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>1337</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>1315</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>0.9835452505609573</v>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>(112785) - Pullman Paris Tour Eiffel</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>1264</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>1254</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>0.9920886075949367</v>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>(111074) - Wyndham Garden Chinatown</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>1218</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>1218</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>(116571) - Conrad Istanbul Bosphorus</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Istanbul Area</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>1193</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>1193</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>(547549) - Crowne Plaza Istanbul Ortakoy Bosphorus by IHG</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Istanbul Area</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>1182</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>1176</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>0.9949238578680203</v>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>(541116) - InterContinental Ras Al Khaimah Mina Al Arab Resort &amp; Spa by IHG</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Ras Al Khaimah Area</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>1178</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>1085</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>0.9210526315789473</v>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>(102019) - Eden Roc Miami Beach</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Best Western</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Miami Area</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>1141</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>1099</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>0.9631901840490797</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>(100091) - All Ritmo Cancún Resort &amp; Waterpark</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>1111</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>(139887) - Jeddah Hilton</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Jeddah Area</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>1086</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>1063</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>0.9788213627992634</v>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>(121774) - Ramses Hilton</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>El Cairo Area</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>1064</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>1062</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>0.9981203007518797</v>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>(111036) - Hyatt Herald Square New York</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>1058</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>1043</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>0.9858223062381852</v>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>(111896) - InterContinental Berlin by IHG</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Berlin Area</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>1007</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>918</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>0.9116186693147964</v>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>(523646) - Tbilisi Philharmonic Hotel by Mercure</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Tbilisi Area</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>995</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>995</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>(463159) - Hampton by Hilton Marjan Island</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Ras Al Khaimah Area</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>992</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>978</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>0.9858870967741935</v>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>(539083) - Hotel Indigo Dubai Downtown by IHG</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Dubai Area</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>985</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>846</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="13" t="n">
+        <v>0.8588832487309644</v>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>(117667) - London Hilton on Park Lane</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Londres</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>959</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>956</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="13" t="n">
+        <v>0.9968717413972888</v>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>(108260) - Hilton Atlanta</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Atlanta Area</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>952</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>921</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="13" t="n">
+        <v>0.967436974789916</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>(541808) - Th8 Palm Dubai Beach Resort, Vignette Collection by IHG</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Dubai Area</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>929</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>842</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="13" t="n">
+        <v>0.9063509149623251</v>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>(113388) - Hilton Los Angeles Airport</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Los Angeles (and vicinity), CA, US</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>921</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>905</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="13" t="n">
+        <v>0.9826275787187839</v>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>(109422) - Disney's Art of Animation Resort</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Disney</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>899</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>897</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="13" t="n">
+        <v>0.9977753058954394</v>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>(239538) - Hilton Garden Inn New York/Times Square Central</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>869</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>869</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>(496363) - Holiday Inn Express Amsterdam - North Riverside by IHG</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>845</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>830</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="13" t="n">
+        <v>0.9822485207100592</v>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>(111047) - Millennium Hilton New York One UN Plaza</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>841</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>711</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="13" t="n">
+        <v>0.845422116527943</v>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>(115833) - SO/ Vienna</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Vienna Area</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>829</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>827</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="13" t="n">
+        <v>0.9975874547647768</v>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>(309176) - Hotel Indigo Los Angeles Downtown by IHG</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Los Angeles (and vicinity), CA, US</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>809</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>448</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="13" t="n">
+        <v>0.553770086526576</v>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>(113661) - Hotel Indigo Venice - Sant'Elena by IHG</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Veneto Area</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>803</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>499</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="13" t="n">
+        <v>0.6214196762141968</v>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>(157062) - Emporio Cancun - with Optional All Inclusive</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Emporio</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>725</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>725</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>(111015) - Gild Hall, A Thompson Hotel, by Hyatt</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>713</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>713</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>(152097) - Fairmont Nile City, Cairo</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>El Cairo Area</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>706</v>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>685</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="13" t="n">
+        <v>0.9702549575070821</v>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>(149317) - JW Marriott Hotel Marina</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Marriott</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Dubai Area</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>691</v>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>691</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>(112090) - InterContinental Bali Resort by IHG</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Bali Area</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>679</v>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>678</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="13" t="n">
+        <v>0.9985272459499264</v>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>(186668) - Holiday Inn Key Largo by IHG</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Key Largo Area</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>677</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>522</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="13" t="n">
+        <v>0.7710487444608567</v>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>(107757) - Kimpton Theta New York - Times Square by IHG</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>674</v>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>552</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="13" t="n">
+        <v>0.8189910979228486</v>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>(135928) - Parklane, a Luxury Collection Resort &amp; Spa, Limassol</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Marriott</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Paphos Area</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>673</v>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>667</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="13" t="n">
+        <v>0.9910846953937593</v>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>(100478) - Presidente InterContinental Cancún</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Presidente Intercontinental</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>648</v>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>600</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="13" t="n">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>(114411) - Hilton Daytona Beach Oceanfront Resort</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Daytona Beach Area</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>644</v>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>641</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="13" t="n">
+        <v>0.9953416149068323</v>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canasta CUG · Severity Eficacia</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CUG (UOP) · P80 · target ≥ 97%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Banda</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Rango</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Hoteles</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>&lt;60%</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.03320108582167467</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>60-85%</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>447</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.0933389016496137</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>85-93%</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>533</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.1112967216537899</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>93-97%</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>637</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.1330131551472124</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>≥97%</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>3013</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.6291501357277093</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canasta CUG · Severity Conv Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CUG (UOP) · P80 · target ≥ 2,5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Banda</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Rango</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Hoteles</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>BKGS=0</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2292</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.4785967842973481</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>&lt;0,8%</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.02422217581958655</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>0,8-1,5%</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>231</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.04823553977865943</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1,5-2,5%</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>342</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.0714136562956776</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>≥2,5%</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1808</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.3775318438087283</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9094,7 +14060,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11155,7 +16121,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11192,7 +16158,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13098,152 +18064,1942 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Severity · ConvRate</t>
+          <t>Canasta CUG · Top 50 Sin Conversión</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P80 · 4734 hoteles · target ≥ 2,5%</t>
+          <t>CUG (UOP) · BKGS=0 · ordenado por CR ↓ · cohorte estructural</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Banda</t>
+          <t>Rk</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Rango</t>
+          <t>Hotel</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Hoteles</t>
+          <t>CorpName</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Destino</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>CR_Unicos</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Bookings</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Eficacia</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>BandaEficacia</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Sin Conversión</t>
-        </is>
+      <c r="A6" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>BKGS=0</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>1342</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>0.2834811998310097</v>
+          <t>(475706) - Conrad Las Vegas at Resorts World</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Las Vegas (and vicinity), NV, US</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>907</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>0.07497243660418963</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>(103023) - Hyatt Regency New Orleans</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>635</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>626</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>0.9858267716535433</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>(107953) - Hilton Garden Inn Chicago Downtown/Magnificent Mile</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>551</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>535</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>0.9709618874773139</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>(103365) - Sheraton New York Times Square Hotel</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Marriott</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>523</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>428</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>0.8183556405353728</v>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>&lt;0,8%</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>813</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>0.1717363751584284</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>(152097) - Fairmont Nile City, Cairo</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>El Cairo Area</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>511</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>475</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>0.9295499021526419</v>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>0,8-1,5%</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>789</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>(103551) - Holiday Inn Toronto Downtown Centre by IHG</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Toronto Area</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>487</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>478</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>0.9815195071868583</v>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>(105001) - InterContinental Miami, an IHG Hotel</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Miami Area</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>449</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>431</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>0.9599109131403119</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>1,5-2,5%</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>713</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>0.1506125897760879</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>(112218) - Mövenpick Hotel Amsterdam City Centre</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>430</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>426</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>0.9906976744186047</v>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>≥2,5%</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>1077</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0.2275031685678074</v>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>(493882) - Holiday Inn Antalya - Lara by IHG</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Antalya Area</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>421</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>417</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>0.9904988123515439</v>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>(520454) - Tribe Amsterdam City</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>397</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>384</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>0.9672544080604534</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>(103363) - The Manhattan at Times Square Hotel</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>394</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>333</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>0.8451776649746193</v>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>(109422) - Disney's Art of Animation Resort</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Disney</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Orlando</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>381</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>378</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>0.9921259842519685</v>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>(100091) - All Ritmo Cancún Resort &amp; Waterpark</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>AA-Independent</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>369</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>(112086) - ibis Milano Centro</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>356</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>348</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>0.9775280898876404</v>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>(112571) - Melia White House</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Melia</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Londres</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>341</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>(102092) - Hilton San Francisco Union Square</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>338</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>337</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>0.9970414201183432</v>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>(104960) - Hilton New York Fashion District</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>336</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>332</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="13" t="n">
+        <v>0.9880952380952381</v>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>(103818) - Iberostar Waves Rose Hall Beach</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Iberostar</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>329</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>(491612) - Waldorf Astoria Dubai International Financial Centre</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Dubai Area</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>321</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>319</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>0.9937694704049844</v>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>(103819) - Iberostar Selection Rose Hall Suites</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Iberostar</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>319</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>(486497) - TRYP By Wyndham Istanbul Sisli Hotel</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Wyndham</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Istanbul Area</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>313</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>313</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>(112576) - Hilton London Metropole</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Londres</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>302</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>298</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>0.9867549668874173</v>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>(131601) - Hilton Toronto/Markham Suites Conference Centre &amp; Spa</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Toronto Area</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>298</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>296</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>0.9932885906040269</v>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>(276943) - Waldorf Astoria Dubai Palm Jumeirah</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Dubai Area</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>292</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>287</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="13" t="n">
+        <v>0.9828767123287672</v>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>(103856) - Novotel London West</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Londres</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>288</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>282</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="13" t="n">
+        <v>0.9791666666666666</v>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>(547549) - Crowne Plaza Istanbul Ortakoy Bosphorus by IHG</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Istanbul Area</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>288</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>287</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="13" t="n">
+        <v>0.9965277777777778</v>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>(111047) - Millennium Hilton New York One UN Plaza</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>279</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>206</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>0.7383512544802867</v>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>(539083) - Hotel Indigo Dubai Downtown by IHG</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Dubai Area</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>274</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>244</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="13" t="n">
+        <v>0.8905109489051095</v>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>(108547) - Hilton Boston Logan Airport</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>274</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>274</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>(121787) - Holiday Inn Cairo Maadi by IHG</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>El Cairo Area</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>272</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>146</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="13" t="n">
+        <v>0.5367647058823529</v>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>(188901) - ANA Crowne Plaza Kanazawa by IHG</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Kanazawa Area</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>270</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>269</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="13" t="n">
+        <v>0.9962962962962963</v>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>(112206) - ibis Amsterdam Centre</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>269</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>261</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="13" t="n">
+        <v>0.9702602230483272</v>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>(103725) - Washington Hilton</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Greenville Area</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>269</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>266</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="13" t="n">
+        <v>0.9888475836431226</v>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>(322551) - Ocean El Faro</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Ocean by H10</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>253</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>205</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="13" t="n">
+        <v>0.8102766798418972</v>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>(102792) - Parc 55 San Francisco - A Hilton Hotel</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>252</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>251</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="13" t="n">
+        <v>0.996031746031746</v>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>(109744) - Holiday Inn NYC - Lower East Side by IHG</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>252</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="13" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>Súper Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>(108214) - Atlanta Marriott Marquis</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Marriott</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Atlanta Area</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>231</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="13" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>(180456) - Holiday Inn Austin -Town Lake by IHG</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>246</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>216</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="13" t="n">
+        <v>0.8780487804878049</v>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>(104976) - The Westin New York Grand Central</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Marriott</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>246</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="13" t="n">
+        <v>0.8943089430894309</v>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>(237935) - Hotel Riu Plaza New York Times Square</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>RIU</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>237</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>235</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="13" t="n">
+        <v>0.9915611814345991</v>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>(108414) - Hyatt Regency DFW International Airport - Adjacent to Terminal C</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>229</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>229</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>(102001) - New York Marriott Marquis</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Marriott</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>224</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>146</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="13" t="n">
+        <v>0.6517857142857143</v>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>(111292) - Mercure Paris Centre Tour Eiffel</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>223</v>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="13" t="n">
+        <v>0.9865470852017937</v>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>(108573) - Fairmont Copley Plaza, Boston</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Accor</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>212</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="13" t="n">
+        <v>0.9636363636363636</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>(228651) - InterContinental Edinburgh The George by IHG</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Edinburgh Area</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>179</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="13" t="n">
+        <v>0.8136363636363636</v>
+      </c>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>(104803) - Hilton Toronto</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Toronto Area</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>217</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>215</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="13" t="n">
+        <v>0.9907834101382489</v>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>(280140) - Hilton Batumi</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Adjara Area</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>214</v>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>193</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="13" t="n">
+        <v>0.9018691588785047</v>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>(149683) - Conrad Abu Dhabi Etihad Towers</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>211</v>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>211</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>(100478) - Presidente InterContinental Cancún</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Presidente Intercontinental</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Cancún</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>206</v>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>191</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="13" t="n">
+        <v>0.9271844660194175</v>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>(485913) - Holiday Inn Express London Heathrow T4</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>IHG</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>London Area</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>204</v>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>199</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="13" t="n">
+        <v>0.9754901960784313</v>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -13290,7 +20046,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -15543,7 +22299,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17486,7 +24242,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -19430,7 +26186,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21428,7 +28184,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23273,7 +30029,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23827,7 +30583,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 04/05/2026 22:05 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 00:31 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-18/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9164,7 +9164,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11007,7 +11007,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11345,7 +11345,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13283,7 +13283,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13436,7 +13436,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13589,7 +13589,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -15846,7 +15846,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17789,7 +17789,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -19732,7 +19732,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21575,7 +21575,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23418,7 +23418,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23861,7 +23861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -25799,7 +25799,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -25959,7 +25959,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28207,7 +28207,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28366,7 +28366,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -30464,7 +30464,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -32407,7 +32407,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -34350,7 +34350,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -36193,7 +36193,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38036,7 +38036,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38514,7 +38514,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -40457,7 +40457,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -42400,7 +42400,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -44344,7 +44344,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -46342,7 +46342,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48187,7 +48187,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48741,7 +48741,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/05/2026 00:57 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 05/05/2026 01:35 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-18/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7973,18 +7973,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8004,7 +8004,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8402,6 +8402,1406 @@
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Cartagena Area</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>4297</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>4139</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>0.9632301605771468</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>0.008145217593670002</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Atlanta Area</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>4295</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>4207</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>0.9795110593713621</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>0.0006984866123399302</v>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Mexico City - Central Mexico</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>3959</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>3807</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>160</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>0.9616064662793635</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>0.04041424602172266</v>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Seattle Area</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>3795</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>3612</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>0.9517786561264822</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>0.0007905138339920949</v>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Houston (and vicinity), TX, US</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>3341</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>3297</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0.9868302903322359</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>0.002095181083507932</v>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Greenville Area</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>3281</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>2915</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0.8884486437061871</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>0.0003047851264858275</v>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>3071</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>2976</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>0.9690654509931619</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>0.001302507326603712</v>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Puerto Vallarta Area</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>3040</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>2962</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0.9743421052631579</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>0.01151315789473684</v>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Denver (and vicinity), CO, US</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>2950</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>2875</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>0.9745762711864406</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>0.0006779661016949153</v>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Nashville (and vicinity), TN, US</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>2893</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>2788</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.9637054960248876</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>0.001036985827860353</v>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Phoenix (and vicinity), AZ, US</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>2785</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>2731</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0.9806104129263914</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>0.000718132854578097</v>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Acapulco</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>2758</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>2642</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>103</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>0.9579405366207396</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>0.03734590282813633</v>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Bogotá Area</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>2745</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>2347</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0.8550091074681239</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>0.02003642987249545</v>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Honolulu Area</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>2660</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>2632</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>0.9894736842105263</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>0.0007518796992481203</v>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Montreal</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>2618</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>2590</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>0.9893048128342246</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>0.001145912910618793</v>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>2592</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>2558</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>0.9868827160493827</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>0.001157407407407407</v>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale (and vicinity), FL, US</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>2577</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>2551</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>0.9899107489328677</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>0.001552192471866511</v>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Niagara Falls, Canada</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>2525</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>2520</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>0.998019801980198</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>0.0003960396039603961</v>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Londres</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>2474</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>2332</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>0.9426030719482619</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>0.0004042037186742118</v>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>2437</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>2415</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>0.9909725071809602</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Riviera Nayarit</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>2051</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>1507</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>0.734763529985373</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>0.003412969283276451</v>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="n">
+        <v>2038</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>0.9906771344455348</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>0.01030421982335623</v>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>1876</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>1852</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>0.9872068230277186</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>0.002132196162046908</v>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>1830</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>1789</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>0.9775956284153006</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>0.000546448087431694</v>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Philadelphia (and vicinity), PA, US</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>1711</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>1677</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>0.9801285797779077</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>1706</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>1643</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>0.9630715123094959</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>0.007033997655334115</v>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Washington, DC Area</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>1534</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>1502</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>0.9791395045632334</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>0.001303780964797914</v>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Ixtapa / Zihuatanejo</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>1486</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>1365</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>0.9185733512786003</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>0.008075370121130552</v>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Area</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>1465</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>1434</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>0.978839590443686</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>0.0006825938566552901</v>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Pittsburgh Area</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="n">
+        <v>1461</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>1446</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>0.9897330595482546</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="n">
+        <v>1444</v>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>1143</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>0.7915512465373962</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>0.04155124653739612</v>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Medellin Area</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>1426</v>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>1358</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>0.9523141654978962</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>0.01332398316970547</v>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Jacksonville Area</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>1321</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>0.9841029523088569</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>0.002271006813020439</v>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Aruba</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n">
+        <v>1271</v>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>1237</v>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>0.973249409913454</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>0.002360346184107002</v>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Anaheim Area</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>1252</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>1236</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>0.987220447284345</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>0.004792332268370607</v>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Minneapolis - St. Paul Area</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="n">
+        <v>1237</v>
+      </c>
+      <c r="D51" s="12" t="n">
+        <v>1214</v>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>0.9814066289409863</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>0.003233629749393694</v>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Detroit Area</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>1209</v>
+      </c>
+      <c r="D52" s="12" t="n">
+        <v>1192</v>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>0.9859387923904053</v>
+      </c>
+      <c r="G52" s="13" t="n">
+        <v>0.001654259718775848</v>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Santa Marta Area</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="n">
+        <v>1156</v>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>1145</v>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>0.990484429065744</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>0.02076124567474048</v>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Mazatlán</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="n">
+        <v>1129</v>
+      </c>
+      <c r="D54" s="12" t="n">
+        <v>1119</v>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>0.9911426040744021</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>0.01505757307351639</v>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>El Cairo Area</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="n">
+        <v>1128</v>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>1074</v>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>0.9521276595744681</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Sin Conversión</t>
         </is>
       </c>
     </row>
@@ -8447,7 +9847,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8785,7 +10185,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10723,7 +12123,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10876,7 +12276,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11029,7 +12429,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11188,7 +12588,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13286,7 +14686,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -15229,7 +16629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -17172,7 +18572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18984,16 +20384,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
@@ -19015,7 +20415,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -19413,6 +20813,1406 @@
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>17781</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>17099</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>285</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>0.9616444519430853</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>0.01602834486249367</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Seattle Area</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>17348</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>16949</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>196</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>0.9770002305741295</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>0.01129813234955038</v>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Dubai Area</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>17231</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>15932</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>0.9246126167953108</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>0.0006964192443851199</v>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>15847</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>15429</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>0.973622767716287</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>0.0008203445447087777</v>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>15303</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>14762</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>185</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0.9646474547474352</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>0.01208913284976802</v>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>El Cairo Area</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>14789</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>13836</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0.935560213672324</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>0.0006085604165257962</v>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Atlanta Area</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>14646</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>14003</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>191</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>0.9560972279120579</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>0.01304110337293459</v>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Los Angeles (and vicinity), CA, US</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>13459</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>12590</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0.9354335388959061</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>0.007355672784010699</v>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>13386</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>13010</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>106</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>0.9719109517406246</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>0.007918721051845212</v>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Houston (and vicinity), TX, US</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>12994</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>12334</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>211</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.9492073264583654</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>0.01623826381406803</v>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Nashville (and vicinity), TN, US</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>12558</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>12155</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>187</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0.9679089026915114</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>0.01489090619525402</v>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>11695</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>11414</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>0.9759726378794357</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>0.00820863616930312</v>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Greenville Area</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>10629</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>9947</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>111</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0.9358359205945996</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>0.0104431272932543</v>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Phoenix (and vicinity), AZ, US</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>10312</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>9980</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>157</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>0.9678044996121024</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>0.01522498060512025</v>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Denver (and vicinity), CO, US</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>10244</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>9805</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>144</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>0.9571456462319406</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>0.01405700898086685</v>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Riviera Nayarit</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>10034</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>7884</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>187</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>0.7857285230217261</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>0.01863663543950568</v>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale (and vicinity), FL, US</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>10017</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>9647</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>0.9630627932514725</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>0.01048218029350105</v>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>9939</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>9764</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>0.9823925948284535</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>0.0003018412315122246</v>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Honolulu Area</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>9636</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>9456</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>88</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>0.9813200498132005</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>0.0091324200913242</v>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Puerto Vallarta Area</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>9565</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>9172</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>0.9589127025614218</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>0.02509147935180345</v>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Punta Cana</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>9266</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>9144</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>103</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>0.9868335851500107</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>0.01111590761925318</v>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="n">
+        <v>8548</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>8188</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>0.957884885353299</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>0.0008189050070191858</v>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>8167</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>7846</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>0.9606954818170687</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>0.01150973429655932</v>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>8074</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>7688</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>155</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>0.9521922219469904</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>0.01919742382957642</v>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Mexico City - Central Mexico</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>7156</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>6845</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>238</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>0.9565399664617105</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>0.03325880380100615</v>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Montreal</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>6888</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>6563</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>0.9528164924506388</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>0.00856562137049942</v>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Edinburgh Area</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>6803</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>6309</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>0.9273849772159342</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>0.01043657210054388</v>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Washington, DC Area</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>6758</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>6649</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>0.9838709677419355</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>0.01627700503107428</v>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>6391</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>6152</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>0.9626036613988421</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>0.006728211547488656</v>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Múnich Area</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="n">
+        <v>6308</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>5606</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>0.888712745719721</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>0.01252377932783767</v>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Berlin Area</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="n">
+        <v>6301</v>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>5931</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>0.9412791620377717</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>0.006189493731153785</v>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Vienna Area</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>6241</v>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>6005</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>0.9621855471879507</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>0.004806921967633392</v>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>6168</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>5834</v>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>0.9458495460440985</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>0.009403372243839169</v>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Tampa Area</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n">
+        <v>6096</v>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>5940</v>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>0.9744094488188977</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>0.01312335958005249</v>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Anaheim Area</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>6068</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>5823</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>0.9596242584047462</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>0.006756756756756757</v>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Cartagena Area</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="n">
+        <v>5996</v>
+      </c>
+      <c r="D51" s="12" t="n">
+        <v>5648</v>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>0.9419613075383589</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>0.01551034022681788</v>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Philadelphia (and vicinity), PA, US</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>5930</v>
+      </c>
+      <c r="D52" s="12" t="n">
+        <v>5740</v>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>0.9679595278246206</v>
+      </c>
+      <c r="G52" s="13" t="n">
+        <v>0.01602023608768971</v>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>London Area</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="n">
+        <v>5557</v>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>5280</v>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>0.9501529602303401</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>0.01007737988123088</v>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="n">
+        <v>5437</v>
+      </c>
+      <c r="D54" s="12" t="n">
+        <v>4993</v>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>0.9183373183741034</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>0.01029979768254552</v>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Minneapolis - St. Paul Area</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="n">
+        <v>5421</v>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>5265</v>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>112</v>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>0.9712230215827338</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>0.02066039476111418</v>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
         </is>
       </c>
     </row>
@@ -19458,7 +22258,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -19901,7 +22701,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21839,7 +24639,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -21998,7 +24798,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -22076,7 +24876,7 @@
       <c r="E6" s="12" t="n">
         <v>640</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="12" t="n">
         <v>51</v>
       </c>
       <c r="G6" s="12" t="n">
@@ -22116,7 +24916,7 @@
       <c r="E7" s="12" t="n">
         <v>6358</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="12" t="n">
         <v>549</v>
       </c>
       <c r="G7" s="12" t="n">
@@ -22156,7 +24956,7 @@
       <c r="E8" s="12" t="n">
         <v>118</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="12" t="n">
         <v>20</v>
       </c>
       <c r="G8" s="12" t="n">
@@ -22196,7 +24996,7 @@
       <c r="E9" s="12" t="n">
         <v>571</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="12" t="n">
         <v>100</v>
       </c>
       <c r="G9" s="12" t="n">
@@ -22236,7 +25036,7 @@
       <c r="E10" s="12" t="n">
         <v>253</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="12" t="n">
         <v>55</v>
       </c>
       <c r="G10" s="12" t="n">
@@ -22276,7 +25076,7 @@
       <c r="E11" s="12" t="n">
         <v>610</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="12" t="n">
         <v>147</v>
       </c>
       <c r="G11" s="12" t="n">
@@ -22316,7 +25116,7 @@
       <c r="E12" s="12" t="n">
         <v>194</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="12" t="n">
         <v>63</v>
       </c>
       <c r="G12" s="12" t="n">
@@ -22356,7 +25156,7 @@
       <c r="E13" s="12" t="n">
         <v>2920</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="12" t="n">
         <v>1116</v>
       </c>
       <c r="G13" s="12" t="n">
@@ -22396,7 +25196,7 @@
       <c r="E14" s="12" t="n">
         <v>392</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="12" t="n">
         <v>151</v>
       </c>
       <c r="G14" s="12" t="n">
@@ -22436,7 +25236,7 @@
       <c r="E15" s="12" t="n">
         <v>454</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="12" t="n">
         <v>176</v>
       </c>
       <c r="G15" s="12" t="n">
@@ -22476,7 +25276,7 @@
       <c r="E16" s="12" t="n">
         <v>740</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="12" t="n">
         <v>296</v>
       </c>
       <c r="G16" s="12" t="n">
@@ -22516,7 +25316,7 @@
       <c r="E17" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="12" t="n">
         <v>56</v>
       </c>
       <c r="G17" s="12" t="n">
@@ -22556,7 +25356,7 @@
       <c r="E18" s="12" t="n">
         <v>123</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F18" s="12" t="n">
         <v>52</v>
       </c>
       <c r="G18" s="12" t="n">
@@ -22596,7 +25396,7 @@
       <c r="E19" s="12" t="n">
         <v>1108</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="12" t="n">
         <v>495</v>
       </c>
       <c r="G19" s="12" t="n">
@@ -22636,7 +25436,7 @@
       <c r="E20" s="12" t="n">
         <v>181</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F20" s="12" t="n">
         <v>82</v>
       </c>
       <c r="G20" s="12" t="n">
@@ -22676,7 +25476,7 @@
       <c r="E21" s="12" t="n">
         <v>137</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F21" s="12" t="n">
         <v>67</v>
       </c>
       <c r="G21" s="12" t="n">
@@ -22716,7 +25516,7 @@
       <c r="E22" s="12" t="n">
         <v>246</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F22" s="12" t="n">
         <v>128</v>
       </c>
       <c r="G22" s="12" t="n">
@@ -22756,7 +25556,7 @@
       <c r="E23" s="12" t="n">
         <v>221</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F23" s="12" t="n">
         <v>115</v>
       </c>
       <c r="G23" s="12" t="n">
@@ -22796,7 +25596,7 @@
       <c r="E24" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="12" t="n">
         <v>48</v>
       </c>
       <c r="G24" s="12" t="n">
@@ -22836,7 +25636,7 @@
       <c r="E25" s="12" t="n">
         <v>273</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" s="12" t="n">
         <v>145</v>
       </c>
       <c r="G25" s="12" t="n">
@@ -22876,7 +25676,7 @@
       <c r="E26" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F26" s="12" t="n">
         <v>52</v>
       </c>
       <c r="G26" s="12" t="n">
@@ -22916,7 +25716,7 @@
       <c r="E27" s="12" t="n">
         <v>230</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="12" t="n">
         <v>127</v>
       </c>
       <c r="G27" s="12" t="n">
@@ -22956,7 +25756,7 @@
       <c r="E28" s="12" t="n">
         <v>263</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F28" s="12" t="n">
         <v>148</v>
       </c>
       <c r="G28" s="12" t="n">
@@ -22996,7 +25796,7 @@
       <c r="E29" s="12" t="n">
         <v>2185</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="12" t="n">
         <v>1231</v>
       </c>
       <c r="G29" s="12" t="n">
@@ -23036,7 +25836,7 @@
       <c r="E30" s="12" t="n">
         <v>1072</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F30" s="12" t="n">
         <v>604</v>
       </c>
       <c r="G30" s="12" t="n">
@@ -23076,7 +25876,7 @@
       <c r="E31" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="F31" s="12" t="n">
         <v>59</v>
       </c>
       <c r="G31" s="12" t="n">
@@ -23116,7 +25916,7 @@
       <c r="E32" s="12" t="n">
         <v>111</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F32" s="12" t="n">
         <v>63</v>
       </c>
       <c r="G32" s="12" t="n">
@@ -23156,7 +25956,7 @@
       <c r="E33" s="12" t="n">
         <v>440</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F33" s="12" t="n">
         <v>252</v>
       </c>
       <c r="G33" s="12" t="n">
@@ -23196,7 +25996,7 @@
       <c r="E34" s="12" t="n">
         <v>1277</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="F34" s="12" t="n">
         <v>733</v>
       </c>
       <c r="G34" s="12" t="n">
@@ -23236,7 +26036,7 @@
       <c r="E35" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="F35" s="12" t="n">
         <v>59</v>
       </c>
       <c r="G35" s="12" t="n">
@@ -23276,7 +26076,7 @@
       <c r="E36" s="12" t="n">
         <v>214</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="F36" s="12" t="n">
         <v>126</v>
       </c>
       <c r="G36" s="12" t="n">
@@ -23316,7 +26116,7 @@
       <c r="E37" s="12" t="n">
         <v>450</v>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="F37" s="12" t="n">
         <v>267</v>
       </c>
       <c r="G37" s="12" t="n">
@@ -23356,7 +26156,7 @@
       <c r="E38" s="12" t="n">
         <v>115</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F38" s="12" t="n">
         <v>69</v>
       </c>
       <c r="G38" s="12" t="n">
@@ -23396,7 +26196,7 @@
       <c r="E39" s="12" t="n">
         <v>285</v>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="F39" s="12" t="n">
         <v>171</v>
       </c>
       <c r="G39" s="12" t="n">
@@ -23436,7 +26236,7 @@
       <c r="E40" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="F40" s="12" t="n">
         <v>65</v>
       </c>
       <c r="G40" s="12" t="n">
@@ -23476,7 +26276,7 @@
       <c r="E41" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="F41" s="5" t="n">
+      <c r="F41" s="12" t="n">
         <v>59</v>
       </c>
       <c r="G41" s="12" t="n">
@@ -23516,7 +26316,7 @@
       <c r="E42" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="F42" s="5" t="n">
+      <c r="F42" s="12" t="n">
         <v>108</v>
       </c>
       <c r="G42" s="12" t="n">
@@ -23556,7 +26356,7 @@
       <c r="E43" s="12" t="n">
         <v>133</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="F43" s="12" t="n">
         <v>82</v>
       </c>
       <c r="G43" s="12" t="n">
@@ -23596,7 +26396,7 @@
       <c r="E44" s="12" t="n">
         <v>348</v>
       </c>
-      <c r="F44" s="5" t="n">
+      <c r="F44" s="12" t="n">
         <v>215</v>
       </c>
       <c r="G44" s="12" t="n">
@@ -23636,7 +26436,7 @@
       <c r="E45" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="12" t="n">
         <v>60</v>
       </c>
       <c r="G45" s="12" t="n">
@@ -23676,7 +26476,7 @@
       <c r="E46" s="12" t="n">
         <v>390</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="F46" s="12" t="n">
         <v>244</v>
       </c>
       <c r="G46" s="12" t="n">
@@ -23716,7 +26516,7 @@
       <c r="E47" s="12" t="n">
         <v>1280</v>
       </c>
-      <c r="F47" s="5" t="n">
+      <c r="F47" s="12" t="n">
         <v>812</v>
       </c>
       <c r="G47" s="12" t="n">
@@ -23756,7 +26556,7 @@
       <c r="E48" s="12" t="n">
         <v>320</v>
       </c>
-      <c r="F48" s="5" t="n">
+      <c r="F48" s="12" t="n">
         <v>204</v>
       </c>
       <c r="G48" s="12" t="n">
@@ -23796,7 +26596,7 @@
       <c r="E49" s="12" t="n">
         <v>218</v>
       </c>
-      <c r="F49" s="5" t="n">
+      <c r="F49" s="12" t="n">
         <v>139</v>
       </c>
       <c r="G49" s="12" t="n">
@@ -23836,7 +26636,7 @@
       <c r="E50" s="12" t="n">
         <v>170</v>
       </c>
-      <c r="F50" s="5" t="n">
+      <c r="F50" s="12" t="n">
         <v>109</v>
       </c>
       <c r="G50" s="12" t="n">
@@ -23876,7 +26676,7 @@
       <c r="E51" s="12" t="n">
         <v>232</v>
       </c>
-      <c r="F51" s="5" t="n">
+      <c r="F51" s="12" t="n">
         <v>149</v>
       </c>
       <c r="G51" s="12" t="n">
@@ -23916,7 +26716,7 @@
       <c r="E52" s="12" t="n">
         <v>168</v>
       </c>
-      <c r="F52" s="5" t="n">
+      <c r="F52" s="12" t="n">
         <v>108</v>
       </c>
       <c r="G52" s="12" t="n">
@@ -23956,7 +26756,7 @@
       <c r="E53" s="12" t="n">
         <v>438</v>
       </c>
-      <c r="F53" s="5" t="n">
+      <c r="F53" s="12" t="n">
         <v>282</v>
       </c>
       <c r="G53" s="12" t="n">
@@ -23996,7 +26796,7 @@
       <c r="E54" s="12" t="n">
         <v>284</v>
       </c>
-      <c r="F54" s="5" t="n">
+      <c r="F54" s="12" t="n">
         <v>184</v>
       </c>
       <c r="G54" s="12" t="n">
@@ -24036,7 +26836,7 @@
       <c r="E55" s="12" t="n">
         <v>303</v>
       </c>
-      <c r="F55" s="5" t="n">
+      <c r="F55" s="12" t="n">
         <v>197</v>
       </c>
       <c r="G55" s="12" t="n">
@@ -24091,7 +26891,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24250,7 +27050,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -26348,7 +29148,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -28291,7 +31091,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -30234,7 +33034,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -32046,11 +34846,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -32077,7 +34877,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -32473,6 +35273,1406 @@
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>5638</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>5365</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>112</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>0.951578573962398</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>0.01986520042568287</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Miami Area</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>5562</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>5375</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>0.9663790003595829</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>0.01330456670262496</v>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Istanbul Area</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>5374</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>5219</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>0.9711574246371418</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>0.002419054707852624</v>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>5090</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>4895</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>0.9616895874263262</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>0.01630648330058939</v>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Toronto Area</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>4839</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>4600</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>0.9506096300888613</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>0.006612936557139905</v>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Cartagena Area</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>4671</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>4569</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>0.9781631342324983</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>0.01605651894669236</v>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Puerto Vallarta Area</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>4422</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>4155</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>207</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>0.9396200814111262</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>0.04681139755766622</v>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Edinburgh Area</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>4376</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>4016</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>0.9177330895795247</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>0.01256855575868373</v>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Atlanta Area</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>4351</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>4089</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>109</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>0.9397839577108711</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>0.02505171225005746</v>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>4351</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>4218</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.9694323144104804</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>0.01907607446564008</v>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Dubai Area</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>4253</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>3913</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0.9200564307547613</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>0.002116153303550435</v>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Riviera Nayarit</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="n">
+        <v>4242</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>3531</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>231</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>0.8323903818953324</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>0.05445544554455446</v>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>El Cairo Area</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>4086</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>3837</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0.9390602055800293</v>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>0.001223690651003426</v>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Seattle Area</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>3954</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>3812</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>0.9640870005058169</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>0.02276176024279211</v>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>3850</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>3496</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>0.908051948051948</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>0.01896103896103896</v>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>3796</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>3181</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>0.8379873551106428</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>0.01422550052687039</v>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Nashville (and vicinity), TN, US</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>3669</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>3506</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>0.9555737258108477</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>0.02098664486236032</v>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>3545</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>3385</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>0.9548660084626234</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>0.01777150916784203</v>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Osaka Area</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>3499</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>3049</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>0.8713918262360675</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>0.01543298085167191</v>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Houston (and vicinity), TX, US</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>3383</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>3149</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>0.9308306237067692</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>0.02335205438959503</v>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>3362</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>3243</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>0.9646044021415824</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>0.01457465794170137</v>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Múnich Area</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="n">
+        <v>3098</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>2753</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>0.8886378308586185</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>0.01484828921885087</v>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>3062</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>2908</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>0.9497060744611365</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>0.003265839320705421</v>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>2890</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>2814</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>0.9737024221453288</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>0.00657439446366782</v>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Ixtapa / Zihuatanejo</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>2533</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>160</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>0.8795138888888889</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Berlin Area</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>2761</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>2588</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>0.9373415429192321</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>0.01412531691416154</v>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Honolulu Area</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>2736</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>2644</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>0.966374269005848</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>0.0135233918128655</v>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Anaheim Area</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>2733</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>2619</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>0.9582875960482986</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>0.01866081229418222</v>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Mexico City - Central Mexico</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>2650</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>2561</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>151</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>0.9664150943396227</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>0.0569811320754717</v>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Phoenix (and vicinity), AZ, US</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="n">
+        <v>2590</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E45" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>0.9652509652509652</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>0.02432432432432433</v>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Greenville Area</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="n">
+        <v>2587</v>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>2277</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>0.8801700811751063</v>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>0.02473908001546192</v>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale (and vicinity), FL, US</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>2443</v>
+      </c>
+      <c r="D47" s="12" t="n">
+        <v>2355</v>
+      </c>
+      <c r="E47" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>0.963978714695047</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>0.0122799836266885</v>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Denver (and vicinity), CO, US</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>2341</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>2222</v>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>0.9491670226398975</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>0.02563007261853908</v>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Puerto Rico</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="n">
+        <v>2232</v>
+      </c>
+      <c r="D49" s="12" t="n">
+        <v>2187</v>
+      </c>
+      <c r="E49" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>0.9798387096774194</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>0.008512544802867384</v>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Manchester Area</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>2224</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>1946</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>0.01888489208633094</v>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>London Area</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="n">
+        <v>2174</v>
+      </c>
+      <c r="D51" s="12" t="n">
+        <v>2050</v>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>0.9429622815087396</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>0.009659613615455382</v>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Vienna Area</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>2079</v>
+      </c>
+      <c r="D52" s="12" t="n">
+        <v>1994</v>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>0.9591149591149591</v>
+      </c>
+      <c r="G52" s="13" t="n">
+        <v>0.01346801346801347</v>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="n">
+        <v>1981</v>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>1885</v>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>0.9515396264512872</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>0.03685007571933367</v>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="n">
+        <v>1961</v>
+      </c>
+      <c r="D54" s="12" t="n">
+        <v>1825</v>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>0.9306476287608363</v>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>0.03008669046404895</v>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Exitosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Los Cabos Area</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="n">
+        <v>1859</v>
+      </c>
+      <c r="D55" s="12" t="n">
+        <v>1660</v>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>0.8929532006455083</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>0.04679935449166218</v>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>Revisar</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -32520,7 +36720,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -32996,7 +37196,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -34939,7 +39139,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -36881,7 +41081,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -38669,7 +42869,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -40512,7 +44712,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -42355,7 +46555,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -42831,7 +47031,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 04:34 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-18/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6161,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8004,7 +8004,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9847,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10185,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12123,7 +12123,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12276,7 +12276,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12429,7 +12429,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12588,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -14686,7 +14686,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18572,7 +18572,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20415,7 +20415,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -22258,7 +22258,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -22701,7 +22701,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24639,7 +24639,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24798,7 +24798,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -26891,7 +26891,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -27050,7 +27050,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29148,7 +29148,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -31091,7 +31091,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33034,7 +33034,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -34877,7 +34877,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -36720,7 +36720,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -37196,7 +37196,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -39139,7 +39139,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -41081,7 +41081,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -42869,7 +42869,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -44712,7 +44712,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -46555,7 +46555,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -47031,7 +47031,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 05:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 05:12 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-18/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-18/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8627,7 +8627,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10850,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13043,7 +13043,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13196,7 +13196,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13349,7 +13349,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -15863,7 +15863,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -18062,7 +18062,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -20260,7 +20260,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -22103,7 +22103,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -23947,7 +23947,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -24446,7 +24446,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -26639,7 +26639,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -26799,7 +26799,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29147,7 +29147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -31661,7 +31661,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -33860,7 +33860,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -36058,7 +36058,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -37901,7 +37901,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -39745,7 +39745,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -40282,7 +40282,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -42481,7 +42481,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -44679,7 +44679,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -46722,7 +46722,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -48565,7 +48565,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -50409,7 +50409,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -50946,7 +50946,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 09/05/2026 14:32 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 09/05/2026 14:42 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
